--- a/Result/profitability/1597.xlsx
+++ b/Result/profitability/1597.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM66"/>
+  <dimension ref="A1:AM67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>0.23625</v>
+        <v>0.3250000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>40.61875</v>
+        <v>40.74375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.49</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2787500000000001</v>
+        <v>0.35</v>
       </c>
       <c r="N3" t="n">
-        <v>39.41125</v>
+        <v>39.43625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.73</v>
       </c>
       <c r="M4" t="n">
-        <v>0.33375</v>
+        <v>0.42125</v>
       </c>
       <c r="N4" t="n">
-        <v>37.92875</v>
+        <v>37.65125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>0.51375</v>
+        <v>0.6200000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>37.0925</v>
+        <v>37.10875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -8812,6 +8812,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1597</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>423</v>
+      </c>
+      <c r="D67" t="n">
+        <v>245</v>
+      </c>
+      <c r="E67" t="n">
+        <v>179</v>
+      </c>
+      <c r="F67" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="G67" t="n">
+        <v>77</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>18.10%</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>24</v>
+      </c>
+      <c r="J67" t="n">
+        <v>100</v>
+      </c>
+      <c r="K67" t="n">
+        <v>75</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="N67" t="n">
+        <v>41.4875</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>0</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
+      </c>
+      <c r="V67" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W67" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="X67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0.4500000000000028</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0.01077586206896552</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>85</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>0.1300000000000026</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>0.003089353612167445</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK67" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
